--- a/AAII_Financials/Yearly/AELIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AELIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>AELIY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -708,7 +708,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>659000</v>
+        <v>660000</v>
       </c>
       <c r="E8" s="3">
         <v>551900</v>
@@ -762,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>344400</v>
+        <v>345300</v>
       </c>
       <c r="E10" s="3">
         <v>222200</v>
@@ -947,7 +947,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>154800</v>
+        <v>155700</v>
       </c>
       <c r="E18" s="3">
         <v>109400</v>
@@ -1014,7 +1014,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>163900</v>
+        <v>164800</v>
       </c>
       <c r="E21" s="3">
         <v>125500</v>
@@ -1040,8 +1040,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>1000</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
@@ -1477,7 +1477,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>90100</v>
+        <v>73800</v>
       </c>
       <c r="E41" s="3">
         <v>56700</v>
@@ -1504,10 +1504,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>274400</v>
+        <v>274700</v>
       </c>
       <c r="E42" s="3">
-        <v>265000</v>
+        <v>264800</v>
       </c>
       <c r="F42" s="3">
         <v>225300</v>
@@ -1531,7 +1531,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6201000</v>
+        <v>6200700</v>
       </c>
       <c r="E43" s="3">
         <v>4550500</v>
@@ -1615,7 +1615,7 @@
         <v>6621800</v>
       </c>
       <c r="E46" s="3">
-        <v>4927300</v>
+        <v>4927100</v>
       </c>
       <c r="F46" s="3">
         <v>4396900</v>
@@ -1642,7 +1642,7 @@
         <v>11700</v>
       </c>
       <c r="E47" s="3">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="F47" s="3">
         <v>4800</v>
@@ -1881,10 +1881,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>879400</v>
+        <v>882300</v>
       </c>
       <c r="E57" s="3">
-        <v>5231600</v>
+        <v>698100</v>
       </c>
       <c r="F57" s="3">
         <v>4592900</v>
@@ -1935,10 +1935,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>74500</v>
+        <v>65800</v>
       </c>
       <c r="E59" s="3">
-        <v>40800</v>
+        <v>40200</v>
       </c>
       <c r="F59" s="3">
         <v>22200</v>
@@ -1965,7 +1965,7 @@
         <v>966100</v>
       </c>
       <c r="E60" s="3">
-        <v>5282500</v>
+        <v>749000</v>
       </c>
       <c r="F60" s="3">
         <v>4650300</v>
@@ -2018,8 +2018,8 @@
       <c r="D62" s="3">
         <v>4700</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
+      <c r="E62" s="3">
+        <v>3500</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>8</v>
@@ -2505,8 +2505,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>2200</v>
       </c>
       <c r="E83" s="3">
         <v>1500</v>
@@ -2708,7 +2708,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1300</v>
+        <v>-700</v>
       </c>
       <c r="E91" s="3">
         <v>-400</v>
